--- a/Team-Data/2008-09/11-20-2008-09.xlsx
+++ b/Team-Data/2008-09/11-20-2008-09.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,22 +806,22 @@
         <v>2.1</v>
       </c>
       <c r="AD2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AE2" t="n">
         <v>9</v>
       </c>
       <c r="AF2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AH2" t="n">
         <v>17</v>
       </c>
       <c r="AI2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AJ2" t="n">
         <v>12</v>
@@ -772,7 +839,7 @@
         <v>2</v>
       </c>
       <c r="AO2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AP2" t="n">
         <v>16</v>
@@ -787,13 +854,13 @@
         <v>19</v>
       </c>
       <c r="AT2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AV2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW2" t="n">
         <v>14</v>
@@ -805,7 +872,7 @@
         <v>18</v>
       </c>
       <c r="AZ2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA2" t="n">
         <v>23</v>
@@ -814,7 +881,7 @@
         <v>7</v>
       </c>
       <c r="BC2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>11-20-2008-09</t>
+          <t>2008-11-20</t>
         </is>
       </c>
     </row>
@@ -858,67 +925,67 @@
         <v>48.4</v>
       </c>
       <c r="I3" t="n">
-        <v>34</v>
+        <v>33.8</v>
       </c>
       <c r="J3" t="n">
-        <v>75.40000000000001</v>
+        <v>75.5</v>
       </c>
       <c r="K3" t="n">
-        <v>0.451</v>
+        <v>0.447</v>
       </c>
       <c r="L3" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="M3" t="n">
         <v>16.3</v>
       </c>
       <c r="N3" t="n">
-        <v>0.332</v>
+        <v>0.311</v>
       </c>
       <c r="O3" t="n">
-        <v>22.8</v>
+        <v>23</v>
       </c>
       <c r="P3" t="n">
-        <v>29.8</v>
+        <v>30.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.765</v>
+        <v>0.758</v>
       </c>
       <c r="R3" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="S3" t="n">
-        <v>33</v>
+        <v>32.6</v>
       </c>
       <c r="T3" t="n">
-        <v>43.9</v>
+        <v>43.4</v>
       </c>
       <c r="U3" t="n">
-        <v>20.8</v>
+        <v>20.3</v>
       </c>
       <c r="V3" t="n">
-        <v>16.9</v>
+        <v>17.3</v>
       </c>
       <c r="W3" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="X3" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="Z3" t="n">
-        <v>23.3</v>
+        <v>24.1</v>
       </c>
       <c r="AA3" t="n">
-        <v>24.9</v>
+        <v>25.3</v>
       </c>
       <c r="AB3" t="n">
-        <v>96.3</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="AC3" t="n">
-        <v>6</v>
+        <v>4.9</v>
       </c>
       <c r="AD3" t="n">
         <v>3</v>
@@ -933,7 +1000,7 @@
         <v>2</v>
       </c>
       <c r="AH3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AI3" t="n">
         <v>27</v>
@@ -942,16 +1009,16 @@
         <v>28</v>
       </c>
       <c r="AK3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AL3" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AM3" t="n">
         <v>16</v>
       </c>
       <c r="AN3" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AO3" t="n">
         <v>3</v>
@@ -960,19 +1027,19 @@
         <v>3</v>
       </c>
       <c r="AQ3" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AR3" t="n">
         <v>19</v>
       </c>
       <c r="AS3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AU3" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AV3" t="n">
         <v>30</v>
@@ -981,19 +1048,19 @@
         <v>4</v>
       </c>
       <c r="AX3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AY3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AZ3" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BA3" t="n">
         <v>3</v>
       </c>
       <c r="BB3" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="BC3" t="n">
         <v>4</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>11-20-2008-09</t>
+          <t>2008-11-20</t>
         </is>
       </c>
     </row>
@@ -1121,10 +1188,10 @@
         <v>30</v>
       </c>
       <c r="AJ4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AK4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL4" t="n">
         <v>27</v>
@@ -1133,16 +1200,16 @@
         <v>27</v>
       </c>
       <c r="AN4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AP4" t="n">
         <v>10</v>
       </c>
       <c r="AQ4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AR4" t="n">
         <v>13</v>
@@ -1157,7 +1224,7 @@
         <v>30</v>
       </c>
       <c r="AV4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AW4" t="n">
         <v>17</v>
@@ -1166,13 +1233,13 @@
         <v>23</v>
       </c>
       <c r="AY4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AZ4" t="n">
         <v>15</v>
       </c>
       <c r="BA4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BB4" t="n">
         <v>30</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>11-20-2008-09</t>
+          <t>2008-11-20</t>
         </is>
       </c>
     </row>
@@ -1207,16 +1274,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F5" t="n">
         <v>7</v>
       </c>
       <c r="G5" t="n">
-        <v>0.364</v>
+        <v>0.417</v>
       </c>
       <c r="H5" t="n">
         <v>48</v>
@@ -1225,76 +1292,76 @@
         <v>34.9</v>
       </c>
       <c r="J5" t="n">
-        <v>85.5</v>
+        <v>84.2</v>
       </c>
       <c r="K5" t="n">
-        <v>0.408</v>
+        <v>0.415</v>
       </c>
       <c r="L5" t="n">
         <v>5</v>
       </c>
       <c r="M5" t="n">
-        <v>15</v>
+        <v>14.8</v>
       </c>
       <c r="N5" t="n">
-        <v>0.333</v>
+        <v>0.339</v>
       </c>
       <c r="O5" t="n">
-        <v>20.8</v>
+        <v>21.8</v>
       </c>
       <c r="P5" t="n">
-        <v>26.1</v>
+        <v>27.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.798</v>
+        <v>0.792</v>
       </c>
       <c r="R5" t="n">
-        <v>13.2</v>
+        <v>13.3</v>
       </c>
       <c r="S5" t="n">
-        <v>31.2</v>
+        <v>30.8</v>
       </c>
       <c r="T5" t="n">
-        <v>44.4</v>
+        <v>44</v>
       </c>
       <c r="U5" t="n">
-        <v>17.7</v>
+        <v>18.5</v>
       </c>
       <c r="V5" t="n">
-        <v>15</v>
+        <v>15.3</v>
       </c>
       <c r="W5" t="n">
         <v>9</v>
       </c>
       <c r="X5" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Y5" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="Z5" t="n">
-        <v>23.2</v>
+        <v>22.8</v>
       </c>
       <c r="AA5" t="n">
-        <v>21.6</v>
+        <v>22.3</v>
       </c>
       <c r="AB5" t="n">
-        <v>95.59999999999999</v>
+        <v>96.7</v>
       </c>
       <c r="AC5" t="n">
-        <v>-4.5</v>
+        <v>-3</v>
       </c>
       <c r="AD5" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="AE5" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="AF5" t="n">
         <v>21</v>
       </c>
       <c r="AG5" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AH5" t="n">
         <v>17</v>
@@ -1303,7 +1370,7 @@
         <v>21</v>
       </c>
       <c r="AJ5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AK5" t="n">
         <v>29</v>
@@ -1312,19 +1379,19 @@
         <v>22</v>
       </c>
       <c r="AM5" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AN5" t="n">
         <v>19</v>
       </c>
       <c r="AO5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP5" t="n">
         <v>8</v>
       </c>
-      <c r="AP5" t="n">
-        <v>15</v>
-      </c>
       <c r="AQ5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AR5" t="n">
         <v>5</v>
@@ -1333,35 +1400,35 @@
         <v>13</v>
       </c>
       <c r="AT5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AU5" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AV5" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AW5" t="n">
         <v>3</v>
       </c>
       <c r="AX5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>29</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>22</v>
+      </c>
+      <c r="BA5" t="n">
         <v>11</v>
       </c>
-      <c r="AY5" t="n">
-        <v>30</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>25</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>14</v>
-      </c>
       <c r="BB5" t="n">
+        <v>18</v>
+      </c>
+      <c r="BC5" t="n">
         <v>22</v>
       </c>
-      <c r="BC5" t="n">
-        <v>24</v>
-      </c>
       <c r="BD5" t="n">
         <v>10</v>
       </c>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>11-20-2008-09</t>
+          <t>2008-11-20</t>
         </is>
       </c>
     </row>
@@ -1389,91 +1456,91 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E6" t="n">
         <v>9</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="H6" t="n">
         <v>48</v>
       </c>
       <c r="I6" t="n">
-        <v>36.6</v>
+        <v>36</v>
       </c>
       <c r="J6" t="n">
-        <v>77.09999999999999</v>
+        <v>76.3</v>
       </c>
       <c r="K6" t="n">
-        <v>0.475</v>
+        <v>0.472</v>
       </c>
       <c r="L6" t="n">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="M6" t="n">
-        <v>19.4</v>
+        <v>19</v>
       </c>
       <c r="N6" t="n">
-        <v>0.362</v>
+        <v>0.351</v>
       </c>
       <c r="O6" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="P6" t="n">
-        <v>27.6</v>
+        <v>28.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.783</v>
+        <v>0.777</v>
       </c>
       <c r="R6" t="n">
-        <v>10.9</v>
+        <v>10.7</v>
       </c>
       <c r="S6" t="n">
-        <v>29.5</v>
+        <v>29.8</v>
       </c>
       <c r="T6" t="n">
         <v>40.4</v>
       </c>
       <c r="U6" t="n">
-        <v>20.4</v>
+        <v>20</v>
       </c>
       <c r="V6" t="n">
-        <v>12.9</v>
+        <v>13.7</v>
       </c>
       <c r="W6" t="n">
         <v>7.8</v>
       </c>
       <c r="X6" t="n">
-        <v>6.3</v>
+        <v>5.9</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="Z6" t="n">
-        <v>21.4</v>
+        <v>21.8</v>
       </c>
       <c r="AA6" t="n">
-        <v>22.4</v>
+        <v>22.8</v>
       </c>
       <c r="AB6" t="n">
-        <v>101.9</v>
+        <v>100.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.800000000000001</v>
+        <v>7.7</v>
       </c>
       <c r="AD6" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="AE6" t="n">
         <v>2</v>
       </c>
       <c r="AF6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG6" t="n">
         <v>3</v>
@@ -1482,22 +1549,22 @@
         <v>17</v>
       </c>
       <c r="AI6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AJ6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK6" t="n">
         <v>3</v>
       </c>
       <c r="AL6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AM6" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AN6" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AO6" t="n">
         <v>4</v>
@@ -1506,37 +1573,37 @@
         <v>7</v>
       </c>
       <c r="AQ6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR6" t="n">
         <v>20</v>
       </c>
       <c r="AS6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT6" t="n">
         <v>19</v>
       </c>
       <c r="AU6" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="AV6" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AW6" t="n">
         <v>11</v>
       </c>
       <c r="AX6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AY6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AZ6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BB6" t="n">
         <v>4</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>11-20-2008-09</t>
+          <t>2008-11-20</t>
         </is>
       </c>
     </row>
@@ -1661,13 +1728,13 @@
         <v>20</v>
       </c>
       <c r="AH7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AI7" t="n">
         <v>8</v>
       </c>
       <c r="AJ7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AK7" t="n">
         <v>22</v>
@@ -1682,13 +1749,13 @@
         <v>27</v>
       </c>
       <c r="AO7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AP7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AQ7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR7" t="n">
         <v>6</v>
@@ -1697,19 +1764,19 @@
         <v>1</v>
       </c>
       <c r="AT7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU7" t="n">
         <v>21</v>
       </c>
       <c r="AV7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AW7" t="n">
         <v>16</v>
       </c>
       <c r="AX7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AY7" t="n">
         <v>8</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>11-20-2008-09</t>
+          <t>2008-11-20</t>
         </is>
       </c>
     </row>
@@ -1837,13 +1904,13 @@
         <v>3</v>
       </c>
       <c r="AF8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AI8" t="n">
         <v>25</v>
@@ -1855,13 +1922,13 @@
         <v>18</v>
       </c>
       <c r="AL8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AM8" t="n">
         <v>19</v>
       </c>
       <c r="AN8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO8" t="n">
         <v>1</v>
@@ -1879,13 +1946,13 @@
         <v>7</v>
       </c>
       <c r="AT8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AU8" t="n">
         <v>7</v>
       </c>
       <c r="AV8" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AW8" t="n">
         <v>2</v>
@@ -1897,13 +1964,13 @@
         <v>27</v>
       </c>
       <c r="AZ8" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BA8" t="n">
         <v>2</v>
       </c>
       <c r="BB8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BC8" t="n">
         <v>9</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>11-20-2008-09</t>
+          <t>2008-11-20</t>
         </is>
       </c>
     </row>
@@ -1935,106 +2002,106 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E9" t="n">
         <v>8</v>
       </c>
       <c r="F9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G9" t="n">
-        <v>0.667</v>
+        <v>0.727</v>
       </c>
       <c r="H9" t="n">
         <v>48</v>
       </c>
       <c r="I9" t="n">
-        <v>35.3</v>
+        <v>35.8</v>
       </c>
       <c r="J9" t="n">
-        <v>78.90000000000001</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>0.447</v>
+        <v>0.448</v>
       </c>
       <c r="L9" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="M9" t="n">
-        <v>15</v>
+        <v>15.2</v>
       </c>
       <c r="N9" t="n">
         <v>0.389</v>
       </c>
       <c r="O9" t="n">
-        <v>20.8</v>
+        <v>21.1</v>
       </c>
       <c r="P9" t="n">
-        <v>26.3</v>
+        <v>26.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.788</v>
+        <v>0.795</v>
       </c>
       <c r="R9" t="n">
-        <v>11.9</v>
+        <v>12.2</v>
       </c>
       <c r="S9" t="n">
-        <v>29.9</v>
+        <v>30.1</v>
       </c>
       <c r="T9" t="n">
-        <v>41.8</v>
+        <v>42.3</v>
       </c>
       <c r="U9" t="n">
-        <v>20.3</v>
+        <v>20.5</v>
       </c>
       <c r="V9" t="n">
-        <v>13.5</v>
+        <v>13.2</v>
       </c>
       <c r="W9" t="n">
         <v>6.8</v>
       </c>
       <c r="X9" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Y9" t="n">
         <v>4.6</v>
       </c>
       <c r="Z9" t="n">
-        <v>22.3</v>
+        <v>22.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>22.3</v>
+        <v>22.7</v>
       </c>
       <c r="AB9" t="n">
-        <v>97.09999999999999</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.3</v>
+        <v>3</v>
       </c>
       <c r="AD9" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="AE9" t="n">
         <v>3</v>
       </c>
       <c r="AF9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AG9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AH9" t="n">
         <v>17</v>
       </c>
       <c r="AI9" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AJ9" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AK9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AL9" t="n">
         <v>14</v>
@@ -2049,25 +2116,25 @@
         <v>9</v>
       </c>
       <c r="AP9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AQ9" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AR9" t="n">
         <v>11</v>
       </c>
       <c r="AS9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AT9" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AU9" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AV9" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AW9" t="n">
         <v>22</v>
@@ -2079,16 +2146,16 @@
         <v>11</v>
       </c>
       <c r="AZ9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA9" t="n">
         <v>10</v>
       </c>
       <c r="BB9" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="BC9" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>11-20-2008-09</t>
+          <t>2008-11-20</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>-0.3</v>
       </c>
       <c r="AD10" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AE10" t="n">
         <v>15</v>
@@ -2213,13 +2280,13 @@
         <v>3</v>
       </c>
       <c r="AJ10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK10" t="n">
         <v>21</v>
       </c>
       <c r="AL10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AM10" t="n">
         <v>13</v>
@@ -2240,7 +2307,7 @@
         <v>1</v>
       </c>
       <c r="AS10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AT10" t="n">
         <v>5</v>
@@ -2261,13 +2328,13 @@
         <v>23</v>
       </c>
       <c r="AZ10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA10" t="n">
         <v>1</v>
       </c>
       <c r="BB10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BC10" t="n">
         <v>17</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>11-20-2008-09</t>
+          <t>2008-11-20</t>
         </is>
       </c>
     </row>
@@ -2386,10 +2453,10 @@
         <v>10</v>
       </c>
       <c r="AG11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AI11" t="n">
         <v>29</v>
@@ -2404,7 +2471,7 @@
         <v>15</v>
       </c>
       <c r="AM11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AN11" t="n">
         <v>18</v>
@@ -2419,7 +2486,7 @@
         <v>1</v>
       </c>
       <c r="AR11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS11" t="n">
         <v>10</v>
@@ -2431,7 +2498,7 @@
         <v>26</v>
       </c>
       <c r="AV11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AW11" t="n">
         <v>19</v>
@@ -2452,7 +2519,7 @@
         <v>26</v>
       </c>
       <c r="BC11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>11-20-2008-09</t>
+          <t>2008-11-20</t>
         </is>
       </c>
     </row>
@@ -2577,10 +2644,10 @@
         <v>6</v>
       </c>
       <c r="AJ12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AK12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AL12" t="n">
         <v>8</v>
@@ -2589,7 +2656,7 @@
         <v>5</v>
       </c>
       <c r="AN12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AO12" t="n">
         <v>22</v>
@@ -2598,22 +2665,22 @@
         <v>23</v>
       </c>
       <c r="AQ12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR12" t="n">
         <v>17</v>
       </c>
       <c r="AS12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AT12" t="n">
         <v>4</v>
       </c>
       <c r="AU12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV12" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AW12" t="n">
         <v>13</v>
@@ -2634,7 +2701,7 @@
         <v>6</v>
       </c>
       <c r="BC12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>11-20-2008-09</t>
+          <t>2008-11-20</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>-9.800000000000001</v>
       </c>
       <c r="AD13" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AE13" t="n">
         <v>27</v>
@@ -2756,7 +2823,7 @@
         <v>6</v>
       </c>
       <c r="AI13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AJ13" t="n">
         <v>9</v>
@@ -2807,7 +2874,7 @@
         <v>15</v>
       </c>
       <c r="AZ13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA13" t="n">
         <v>26</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>11-20-2008-09</t>
+          <t>2008-11-20</t>
         </is>
       </c>
     </row>
@@ -2860,67 +2927,67 @@
         <v>48</v>
       </c>
       <c r="I14" t="n">
-        <v>39</v>
+        <v>38.4</v>
       </c>
       <c r="J14" t="n">
-        <v>87.40000000000001</v>
+        <v>86.2</v>
       </c>
       <c r="K14" t="n">
         <v>0.446</v>
       </c>
       <c r="L14" t="n">
-        <v>6.7</v>
+        <v>6.3</v>
       </c>
       <c r="M14" t="n">
-        <v>17.7</v>
+        <v>16.4</v>
       </c>
       <c r="N14" t="n">
-        <v>0.377</v>
+        <v>0.385</v>
       </c>
       <c r="O14" t="n">
-        <v>21.2</v>
+        <v>21.7</v>
       </c>
       <c r="P14" t="n">
-        <v>28.1</v>
+        <v>28.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.755</v>
+        <v>0.759</v>
       </c>
       <c r="R14" t="n">
         <v>14</v>
       </c>
       <c r="S14" t="n">
-        <v>33</v>
+        <v>33.9</v>
       </c>
       <c r="T14" t="n">
-        <v>47</v>
+        <v>47.9</v>
       </c>
       <c r="U14" t="n">
-        <v>22</v>
+        <v>21.3</v>
       </c>
       <c r="V14" t="n">
-        <v>13.3</v>
+        <v>14.2</v>
       </c>
       <c r="W14" t="n">
-        <v>10.4</v>
+        <v>10.7</v>
       </c>
       <c r="X14" t="n">
-        <v>6.3</v>
+        <v>6.6</v>
       </c>
       <c r="Y14" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Z14" t="n">
-        <v>21.2</v>
+        <v>21</v>
       </c>
       <c r="AA14" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="AB14" t="n">
-        <v>105.9</v>
+        <v>104.9</v>
       </c>
       <c r="AC14" t="n">
-        <v>12.8</v>
+        <v>13.6</v>
       </c>
       <c r="AD14" t="n">
         <v>29</v>
@@ -2938,10 +3005,10 @@
         <v>17</v>
       </c>
       <c r="AI14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK14" t="n">
         <v>13</v>
@@ -2950,34 +3017,34 @@
         <v>11</v>
       </c>
       <c r="AM14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AN14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AO14" t="n">
         <v>6</v>
       </c>
       <c r="AP14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ14" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AR14" t="n">
         <v>3</v>
       </c>
       <c r="AS14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AT14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AU14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV14" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AW14" t="n">
         <v>1</v>
@@ -2986,16 +3053,16 @@
         <v>4</v>
       </c>
       <c r="AY14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BB14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BC14" t="n">
         <v>1</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>11-20-2008-09</t>
+          <t>2008-11-20</t>
         </is>
       </c>
     </row>
@@ -3105,16 +3172,16 @@
         <v>-3.8</v>
       </c>
       <c r="AD15" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AE15" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AF15" t="n">
         <v>21</v>
       </c>
       <c r="AG15" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AH15" t="n">
         <v>6</v>
@@ -3123,7 +3190,7 @@
         <v>24</v>
       </c>
       <c r="AJ15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AK15" t="n">
         <v>19</v>
@@ -3132,19 +3199,19 @@
         <v>23</v>
       </c>
       <c r="AM15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AN15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO15" t="n">
         <v>12</v>
       </c>
       <c r="AP15" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AQ15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR15" t="n">
         <v>22</v>
@@ -3171,16 +3238,16 @@
         <v>14</v>
       </c>
       <c r="AZ15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BB15" t="n">
         <v>23</v>
       </c>
       <c r="BC15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>11-20-2008-09</t>
+          <t>2008-11-20</t>
         </is>
       </c>
     </row>
@@ -3302,13 +3369,13 @@
         <v>17</v>
       </c>
       <c r="AI16" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AJ16" t="n">
         <v>13</v>
       </c>
       <c r="AK16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL16" t="n">
         <v>5</v>
@@ -3323,7 +3390,7 @@
         <v>24</v>
       </c>
       <c r="AP16" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AQ16" t="n">
         <v>25</v>
@@ -3338,7 +3405,7 @@
         <v>23</v>
       </c>
       <c r="AU16" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AV16" t="n">
         <v>4</v>
@@ -3347,7 +3414,7 @@
         <v>5</v>
       </c>
       <c r="AX16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AY16" t="n">
         <v>4</v>
@@ -3362,7 +3429,7 @@
         <v>14</v>
       </c>
       <c r="BC16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>11-20-2008-09</t>
+          <t>2008-11-20</t>
         </is>
       </c>
     </row>
@@ -3391,28 +3458,28 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E17" t="n">
         <v>5</v>
       </c>
       <c r="F17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G17" t="n">
-        <v>0.417</v>
+        <v>0.385</v>
       </c>
       <c r="H17" t="n">
-        <v>49.3</v>
+        <v>49.2</v>
       </c>
       <c r="I17" t="n">
-        <v>35.1</v>
+        <v>35.2</v>
       </c>
       <c r="J17" t="n">
-        <v>82.3</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>0.427</v>
+        <v>0.43</v>
       </c>
       <c r="L17" t="n">
         <v>5.3</v>
@@ -3421,34 +3488,34 @@
         <v>14.2</v>
       </c>
       <c r="N17" t="n">
-        <v>0.371</v>
+        <v>0.375</v>
       </c>
       <c r="O17" t="n">
-        <v>20.3</v>
+        <v>19.8</v>
       </c>
       <c r="P17" t="n">
-        <v>26.9</v>
+        <v>26.4</v>
       </c>
       <c r="Q17" t="n">
         <v>0.752</v>
       </c>
       <c r="R17" t="n">
-        <v>13.7</v>
+        <v>13.6</v>
       </c>
       <c r="S17" t="n">
-        <v>30.8</v>
+        <v>29.9</v>
       </c>
       <c r="T17" t="n">
-        <v>44.5</v>
+        <v>43.5</v>
       </c>
       <c r="U17" t="n">
         <v>20.6</v>
       </c>
       <c r="V17" t="n">
-        <v>16.3</v>
+        <v>16.5</v>
       </c>
       <c r="W17" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="X17" t="n">
         <v>3.3</v>
@@ -3457,55 +3524,55 @@
         <v>5.8</v>
       </c>
       <c r="Z17" t="n">
-        <v>25.9</v>
+        <v>26.2</v>
       </c>
       <c r="AA17" t="n">
-        <v>24.9</v>
+        <v>24.4</v>
       </c>
       <c r="AB17" t="n">
-        <v>95.7</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="AC17" t="n">
-        <v>-1.6</v>
+        <v>-2.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE17" t="n">
         <v>15</v>
       </c>
       <c r="AF17" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AG17" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AH17" t="n">
         <v>2</v>
       </c>
       <c r="AI17" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AJ17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AK17" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL17" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AM17" t="n">
         <v>26</v>
       </c>
       <c r="AN17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AO17" t="n">
+        <v>14</v>
+      </c>
+      <c r="AP17" t="n">
         <v>13</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>9</v>
       </c>
       <c r="AQ17" t="n">
         <v>21</v>
@@ -3514,16 +3581,16 @@
         <v>4</v>
       </c>
       <c r="AS17" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AT17" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AU17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AV17" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AW17" t="n">
         <v>29</v>
@@ -3538,7 +3605,7 @@
         <v>30</v>
       </c>
       <c r="BA17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BB17" t="n">
         <v>21</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>11-20-2008-09</t>
+          <t>2008-11-20</t>
         </is>
       </c>
     </row>
@@ -3657,7 +3724,7 @@
         <v>27</v>
       </c>
       <c r="AF18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AG18" t="n">
         <v>27</v>
@@ -3684,13 +3751,13 @@
         <v>29</v>
       </c>
       <c r="AO18" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP18" t="n">
         <v>24</v>
       </c>
       <c r="AQ18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AR18" t="n">
         <v>17</v>
@@ -3717,7 +3784,7 @@
         <v>22</v>
       </c>
       <c r="AZ18" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BA18" t="n">
         <v>18</v>
@@ -3726,7 +3793,7 @@
         <v>15</v>
       </c>
       <c r="BC18" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BD18" t="n">
         <v>10</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>11-20-2008-09</t>
+          <t>2008-11-20</t>
         </is>
       </c>
     </row>
@@ -3836,7 +3903,7 @@
         <v>24</v>
       </c>
       <c r="AE19" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AF19" t="n">
         <v>16</v>
@@ -3863,16 +3930,16 @@
         <v>11</v>
       </c>
       <c r="AN19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AO19" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AP19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AR19" t="n">
         <v>15</v>
@@ -3884,10 +3951,10 @@
         <v>20</v>
       </c>
       <c r="AU19" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AV19" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AW19" t="n">
         <v>23</v>
@@ -3902,7 +3969,7 @@
         <v>29</v>
       </c>
       <c r="BA19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BB19" t="n">
         <v>19</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>11-20-2008-09</t>
+          <t>2008-11-20</t>
         </is>
       </c>
     </row>
@@ -4036,16 +4103,16 @@
         <v>27</v>
       </c>
       <c r="AK20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AL20" t="n">
         <v>6</v>
       </c>
       <c r="AM20" t="n">
+        <v>8</v>
+      </c>
+      <c r="AN20" t="n">
         <v>9</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>8</v>
       </c>
       <c r="AO20" t="n">
         <v>25</v>
@@ -4054,7 +4121,7 @@
         <v>26</v>
       </c>
       <c r="AQ20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AR20" t="n">
         <v>25</v>
@@ -4066,10 +4133,10 @@
         <v>29</v>
       </c>
       <c r="AU20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AV20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW20" t="n">
         <v>8</v>
@@ -4078,7 +4145,7 @@
         <v>26</v>
       </c>
       <c r="AY20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AZ20" t="n">
         <v>9</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>11-20-2008-09</t>
+          <t>2008-11-20</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>-0.6</v>
       </c>
       <c r="AD21" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AE21" t="n">
         <v>12</v>
@@ -4212,7 +4279,7 @@
         <v>6</v>
       </c>
       <c r="AI21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AJ21" t="n">
         <v>1</v>
@@ -4227,7 +4294,7 @@
         <v>1</v>
       </c>
       <c r="AN21" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AO21" t="n">
         <v>28</v>
@@ -4236,13 +4303,13 @@
         <v>28</v>
       </c>
       <c r="AQ21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AR21" t="n">
         <v>23</v>
       </c>
       <c r="AS21" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AT21" t="n">
         <v>17</v>
@@ -4260,7 +4327,7 @@
         <v>30</v>
       </c>
       <c r="AY21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ21" t="n">
         <v>7</v>
@@ -4269,7 +4336,7 @@
         <v>29</v>
       </c>
       <c r="BB21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BC21" t="n">
         <v>18</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>11-20-2008-09</t>
+          <t>2008-11-20</t>
         </is>
       </c>
     </row>
@@ -4397,7 +4464,7 @@
         <v>22</v>
       </c>
       <c r="AJ22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK22" t="n">
         <v>30</v>
@@ -4409,7 +4476,7 @@
         <v>30</v>
       </c>
       <c r="AN22" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO22" t="n">
         <v>26</v>
@@ -4418,7 +4485,7 @@
         <v>21</v>
       </c>
       <c r="AQ22" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR22" t="n">
         <v>6</v>
@@ -4427,7 +4494,7 @@
         <v>8</v>
       </c>
       <c r="AT22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AU22" t="n">
         <v>27</v>
@@ -4445,7 +4512,7 @@
         <v>28</v>
       </c>
       <c r="AZ22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BA22" t="n">
         <v>28</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>11-20-2008-09</t>
+          <t>2008-11-20</t>
         </is>
       </c>
     </row>
@@ -4561,13 +4628,13 @@
         <v>6.4</v>
       </c>
       <c r="AD23" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AE23" t="n">
         <v>3</v>
       </c>
       <c r="AF23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AG23" t="n">
         <v>4</v>
@@ -4576,22 +4643,22 @@
         <v>17</v>
       </c>
       <c r="AI23" t="n">
+        <v>16</v>
+      </c>
+      <c r="AJ23" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>14</v>
       </c>
       <c r="AK23" t="n">
         <v>17</v>
       </c>
       <c r="AL23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM23" t="n">
         <v>2</v>
       </c>
       <c r="AN23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO23" t="n">
         <v>11</v>
@@ -4609,28 +4676,28 @@
         <v>6</v>
       </c>
       <c r="AT23" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AU23" t="n">
         <v>28</v>
       </c>
       <c r="AV23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW23" t="n">
         <v>12</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>11</v>
       </c>
       <c r="AX23" t="n">
         <v>1</v>
       </c>
       <c r="AY23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AZ23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA23" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BB23" t="n">
         <v>8</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>11-20-2008-09</t>
+          <t>2008-11-20</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>2.7</v>
       </c>
       <c r="AD24" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AE24" t="n">
         <v>15</v>
@@ -4761,7 +4828,7 @@
         <v>5</v>
       </c>
       <c r="AJ24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AK24" t="n">
         <v>14</v>
@@ -4773,7 +4840,7 @@
         <v>28</v>
       </c>
       <c r="AN24" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AO24" t="n">
         <v>27</v>
@@ -4794,10 +4861,10 @@
         <v>1</v>
       </c>
       <c r="AU24" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AV24" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AW24" t="n">
         <v>25</v>
@@ -4815,10 +4882,10 @@
         <v>27</v>
       </c>
       <c r="BB24" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BC24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BD24" t="n">
         <v>10</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>11-20-2008-09</t>
+          <t>2008-11-20</t>
         </is>
       </c>
     </row>
@@ -4847,103 +4914,103 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E25" t="n">
         <v>8</v>
       </c>
       <c r="F25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G25" t="n">
-        <v>0.615</v>
+        <v>0.667</v>
       </c>
       <c r="H25" t="n">
         <v>48.4</v>
       </c>
       <c r="I25" t="n">
-        <v>36.5</v>
+        <v>36.4</v>
       </c>
       <c r="J25" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="K25" t="n">
-        <v>0.494</v>
+        <v>0.499</v>
       </c>
       <c r="L25" t="n">
         <v>6.1</v>
       </c>
       <c r="M25" t="n">
-        <v>16.2</v>
+        <v>16</v>
       </c>
       <c r="N25" t="n">
-        <v>0.376</v>
+        <v>0.38</v>
       </c>
       <c r="O25" t="n">
-        <v>20.7</v>
+        <v>21.6</v>
       </c>
       <c r="P25" t="n">
-        <v>27.8</v>
+        <v>28.9</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.743</v>
+        <v>0.746</v>
       </c>
       <c r="R25" t="n">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="S25" t="n">
-        <v>31.5</v>
+        <v>31.3</v>
       </c>
       <c r="T25" t="n">
-        <v>39.8</v>
+        <v>39.3</v>
       </c>
       <c r="U25" t="n">
-        <v>20.1</v>
+        <v>19.9</v>
       </c>
       <c r="V25" t="n">
-        <v>16.6</v>
+        <v>16.8</v>
       </c>
       <c r="W25" t="n">
-        <v>6.1</v>
+        <v>6.3</v>
       </c>
       <c r="X25" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Y25" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Z25" t="n">
-        <v>20.4</v>
+        <v>20.8</v>
       </c>
       <c r="AA25" t="n">
-        <v>22.8</v>
+        <v>23.1</v>
       </c>
       <c r="AB25" t="n">
-        <v>99.8</v>
+        <v>100.5</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="AD25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE25" t="n">
         <v>3</v>
       </c>
       <c r="AF25" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG25" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AH25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AI25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AJ25" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AK25" t="n">
         <v>1</v>
@@ -4955,28 +5022,28 @@
         <v>18</v>
       </c>
       <c r="AN25" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AO25" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AP25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AQ25" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AR25" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AS25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AT25" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AU25" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AV25" t="n">
         <v>29</v>
@@ -4988,19 +5055,19 @@
         <v>17</v>
       </c>
       <c r="AY25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ25" t="n">
         <v>8</v>
       </c>
       <c r="BA25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BB25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BC25" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>11-20-2008-09</t>
+          <t>2008-11-20</t>
         </is>
       </c>
     </row>
@@ -5029,124 +5096,124 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E26" t="n">
         <v>7</v>
       </c>
       <c r="F26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G26" t="n">
-        <v>0.636</v>
+        <v>0.583</v>
       </c>
       <c r="H26" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
       <c r="I26" t="n">
-        <v>36</v>
+        <v>35.4</v>
       </c>
       <c r="J26" t="n">
-        <v>78.40000000000001</v>
+        <v>78.8</v>
       </c>
       <c r="K26" t="n">
-        <v>0.459</v>
+        <v>0.449</v>
       </c>
       <c r="L26" t="n">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M26" t="n">
-        <v>19.3</v>
+        <v>19.7</v>
       </c>
       <c r="N26" t="n">
-        <v>0.42</v>
+        <v>0.419</v>
       </c>
       <c r="O26" t="n">
-        <v>19.2</v>
+        <v>18.3</v>
       </c>
       <c r="P26" t="n">
-        <v>24.6</v>
+        <v>23.8</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.779</v>
+        <v>0.768</v>
       </c>
       <c r="R26" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="S26" t="n">
-        <v>27.4</v>
+        <v>27.7</v>
       </c>
       <c r="T26" t="n">
-        <v>39.5</v>
+        <v>39.9</v>
       </c>
       <c r="U26" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="V26" t="n">
-        <v>12.3</v>
+        <v>12.4</v>
       </c>
       <c r="W26" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="X26" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="Y26" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>97.3</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD26" t="n">
         <v>3</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>99.3</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>12</v>
       </c>
       <c r="AE26" t="n">
         <v>9</v>
       </c>
       <c r="AF26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AG26" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AH26" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AI26" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AJ26" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AK26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AL26" t="n">
         <v>3</v>
       </c>
       <c r="AM26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AN26" t="n">
         <v>1</v>
       </c>
       <c r="AO26" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AP26" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AQ26" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AR26" t="n">
         <v>10</v>
@@ -5155,34 +5222,34 @@
         <v>29</v>
       </c>
       <c r="AT26" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AU26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AV26" t="n">
         <v>1</v>
       </c>
       <c r="AW26" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AX26" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AY26" t="n">
         <v>1</v>
       </c>
       <c r="AZ26" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="BA26" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="BB26" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="BC26" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>11-20-2008-09</t>
+          <t>2008-11-20</t>
         </is>
       </c>
     </row>
@@ -5295,19 +5362,19 @@
         <v>15</v>
       </c>
       <c r="AF27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AG27" t="n">
         <v>23</v>
       </c>
       <c r="AH27" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI27" t="n">
         <v>4</v>
       </c>
       <c r="AJ27" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK27" t="n">
         <v>2</v>
@@ -5328,7 +5395,7 @@
         <v>27</v>
       </c>
       <c r="AQ27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AR27" t="n">
         <v>27</v>
@@ -5340,7 +5407,7 @@
         <v>27</v>
       </c>
       <c r="AU27" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AV27" t="n">
         <v>22</v>
@@ -5352,10 +5419,10 @@
         <v>25</v>
       </c>
       <c r="AY27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ27" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BA27" t="n">
         <v>20</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>11-20-2008-09</t>
+          <t>2008-11-20</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>-2.7</v>
       </c>
       <c r="AD28" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AE28" t="n">
         <v>15</v>
@@ -5486,22 +5553,22 @@
         <v>3</v>
       </c>
       <c r="AI28" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AJ28" t="n">
         <v>24</v>
       </c>
       <c r="AK28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AL28" t="n">
         <v>7</v>
       </c>
       <c r="AM28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AN28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AO28" t="n">
         <v>30</v>
@@ -5510,19 +5577,19 @@
         <v>30</v>
       </c>
       <c r="AQ28" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AR28" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AS28" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AT28" t="n">
         <v>26</v>
       </c>
       <c r="AU28" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AV28" t="n">
         <v>2</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>11-20-2008-09</t>
+          <t>2008-11-20</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>-0.8</v>
       </c>
       <c r="AD29" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AE29" t="n">
         <v>12</v>
@@ -5668,13 +5735,13 @@
         <v>6</v>
       </c>
       <c r="AI29" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AJ29" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AL29" t="n">
         <v>12</v>
@@ -5698,10 +5765,10 @@
         <v>28</v>
       </c>
       <c r="AS29" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AT29" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AU29" t="n">
         <v>4</v>
@@ -5713,7 +5780,7 @@
         <v>27</v>
       </c>
       <c r="AX29" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AY29" t="n">
         <v>25</v>
@@ -5722,7 +5789,7 @@
         <v>1</v>
       </c>
       <c r="BA29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BB29" t="n">
         <v>20</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>11-20-2008-09</t>
+          <t>2008-11-20</t>
         </is>
       </c>
     </row>
@@ -5841,10 +5908,10 @@
         <v>3</v>
       </c>
       <c r="AF30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH30" t="n">
         <v>17</v>
@@ -5853,7 +5920,7 @@
         <v>9</v>
       </c>
       <c r="AJ30" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AK30" t="n">
         <v>4</v>
@@ -5868,34 +5935,34 @@
         <v>16</v>
       </c>
       <c r="AO30" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AP30" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AQ30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR30" t="n">
         <v>8</v>
       </c>
       <c r="AS30" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AT30" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AU30" t="n">
         <v>2</v>
       </c>
       <c r="AV30" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW30" t="n">
         <v>5</v>
       </c>
       <c r="AX30" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AY30" t="n">
         <v>24</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>11-20-2008-09</t>
+          <t>2008-11-20</t>
         </is>
       </c>
     </row>
@@ -6023,7 +6090,7 @@
         <v>29</v>
       </c>
       <c r="AF31" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AG31" t="n">
         <v>29</v>
@@ -6035,7 +6102,7 @@
         <v>26</v>
       </c>
       <c r="AJ31" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK31" t="n">
         <v>23</v>
@@ -6068,10 +6135,10 @@
         <v>28</v>
       </c>
       <c r="AU31" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AV31" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW31" t="n">
         <v>10</v>
@@ -6086,7 +6153,7 @@
         <v>5</v>
       </c>
       <c r="BA31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BB31" t="n">
         <v>25</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>11-20-2008-09</t>
+          <t>2008-11-20</t>
         </is>
       </c>
     </row>
